--- a/data/清远/OTA对账/抖音.xlsx
+++ b/data/清远/OTA对账/抖音.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12200"/>
+    <workbookView xWindow="16460" yWindow="5680" windowWidth="9140" windowHeight="6520"/>
   </bookViews>
   <sheets>
     <sheet name="抖音" sheetId="1" r:id="rId1"/>
@@ -1375,7 +1375,7 @@
     <col min="26" max="26" width="11.3727272727273" customWidth="1"/>
     <col min="27" max="27" width="20.1272727272727" customWidth="1"/>
     <col min="28" max="28" width="13.1272727272727" customWidth="1"/>
-    <col min="29" max="29" width="11.3727272727273" customWidth="1"/>
+    <col min="29" max="29" width="36.5454545454545" customWidth="1"/>
     <col min="30" max="30" width="64.7545454545455" customWidth="1"/>
     <col min="31" max="31" width="9.62727272727273" customWidth="1"/>
     <col min="32" max="32" width="13.1272727272727" customWidth="1"/>

--- a/data/清远/OTA对账/抖音.xlsx
+++ b/data/清远/OTA对账/抖音.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\larfe\Qingyuan\data\清远\OTA对账\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F436BE9-F92C-435E-A624-9FFDD395811E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16460" yWindow="5680" windowWidth="9140" windowHeight="6520"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="抖音" sheetId="1" r:id="rId1"/>
@@ -389,14 +395,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -405,345 +405,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -751,311 +427,25 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1340,85 +730,86 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BV13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5" customWidth="1"/>
-    <col min="2" max="2" width="21.6272727272727" customWidth="1"/>
-    <col min="3" max="3" width="30.6363636363636" customWidth="1"/>
+    <col min="1" max="1" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="21.6328125" customWidth="1"/>
+    <col min="3" max="3" width="30.6328125" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
     <col min="5" max="5" width="35" customWidth="1"/>
-    <col min="6" max="6" width="7.87272727272727" customWidth="1"/>
-    <col min="7" max="7" width="11.3727272727273" customWidth="1"/>
-    <col min="8" max="8" width="9.62727272727273" customWidth="1"/>
-    <col min="9" max="9" width="7.87272727272727" customWidth="1"/>
-    <col min="10" max="10" width="13.1272727272727" customWidth="1"/>
-    <col min="11" max="11" width="17.5" customWidth="1"/>
-    <col min="12" max="12" width="11.3727272727273" customWidth="1"/>
-    <col min="14" max="14" width="77.8727272727273" customWidth="1"/>
-    <col min="15" max="15" width="16.6272727272727" customWidth="1"/>
-    <col min="16" max="16" width="14.8727272727273" customWidth="1"/>
-    <col min="17" max="17" width="38.5" customWidth="1"/>
-    <col min="18" max="18" width="28.8727272727273" customWidth="1"/>
-    <col min="19" max="19" width="17.5" customWidth="1"/>
-    <col min="20" max="20" width="7.87272727272727" customWidth="1"/>
-    <col min="21" max="21" width="9.62727272727273" customWidth="1"/>
-    <col min="22" max="22" width="11.3727272727273" customWidth="1"/>
-    <col min="24" max="24" width="14.8727272727273" customWidth="1"/>
-    <col min="25" max="25" width="77.8727272727273" customWidth="1"/>
-    <col min="26" max="26" width="11.3727272727273" customWidth="1"/>
-    <col min="27" max="27" width="20.1272727272727" customWidth="1"/>
-    <col min="28" max="28" width="13.1272727272727" customWidth="1"/>
-    <col min="29" max="29" width="36.5454545454545" customWidth="1"/>
-    <col min="30" max="30" width="64.7545454545455" customWidth="1"/>
-    <col min="31" max="31" width="9.62727272727273" customWidth="1"/>
-    <col min="32" max="32" width="13.1272727272727" customWidth="1"/>
-    <col min="33" max="33" width="23.6272727272727" customWidth="1"/>
-    <col min="34" max="34" width="28.8727272727273" customWidth="1"/>
-    <col min="35" max="35" width="13.1272727272727" customWidth="1"/>
-    <col min="37" max="37" width="16.6272727272727" customWidth="1"/>
-    <col min="38" max="38" width="9.62727272727273" customWidth="1"/>
-    <col min="39" max="39" width="13.1272727272727" customWidth="1"/>
+    <col min="6" max="6" width="7.90625" customWidth="1"/>
+    <col min="7" max="7" width="11.36328125" customWidth="1"/>
+    <col min="8" max="8" width="9.6328125" customWidth="1"/>
+    <col min="9" max="9" width="7.90625" customWidth="1"/>
+    <col min="10" max="10" width="13.08984375" customWidth="1"/>
+    <col min="11" max="11" width="17.453125" customWidth="1"/>
+    <col min="12" max="12" width="11.36328125" customWidth="1"/>
+    <col min="14" max="14" width="77.90625" customWidth="1"/>
+    <col min="15" max="15" width="16.6328125" customWidth="1"/>
+    <col min="16" max="16" width="14.90625" customWidth="1"/>
+    <col min="17" max="17" width="38.453125" customWidth="1"/>
+    <col min="18" max="18" width="28.90625" customWidth="1"/>
+    <col min="19" max="19" width="17.453125" customWidth="1"/>
+    <col min="20" max="20" width="7.90625" customWidth="1"/>
+    <col min="21" max="21" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.36328125" customWidth="1"/>
+    <col min="23" max="23" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.90625" customWidth="1"/>
+    <col min="25" max="25" width="77.90625" customWidth="1"/>
+    <col min="26" max="26" width="11.36328125" customWidth="1"/>
+    <col min="27" max="27" width="20.08984375" customWidth="1"/>
+    <col min="28" max="28" width="13.08984375" customWidth="1"/>
+    <col min="29" max="29" width="36.54296875" customWidth="1"/>
+    <col min="30" max="30" width="64.7265625" customWidth="1"/>
+    <col min="31" max="31" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="28.90625" customWidth="1"/>
+    <col min="35" max="35" width="13.08984375" customWidth="1"/>
+    <col min="37" max="37" width="16.6328125" customWidth="1"/>
+    <col min="38" max="38" width="9.6328125" customWidth="1"/>
+    <col min="39" max="39" width="13.08984375" customWidth="1"/>
     <col min="40" max="40" width="7" customWidth="1"/>
-    <col min="41" max="41" width="9.62727272727273" customWidth="1"/>
-    <col min="42" max="42" width="72.6272727272727" customWidth="1"/>
-    <col min="43" max="43" width="9.62727272727273" customWidth="1"/>
-    <col min="44" max="44" width="11.3727272727273" customWidth="1"/>
-    <col min="45" max="45" width="14.8727272727273" customWidth="1"/>
-    <col min="46" max="46" width="25.3727272727273" customWidth="1"/>
-    <col min="47" max="47" width="9.62727272727273" customWidth="1"/>
-    <col min="48" max="48" width="13.1272727272727" customWidth="1"/>
+    <col min="41" max="41" width="9.6328125" customWidth="1"/>
+    <col min="42" max="42" width="72.6328125" customWidth="1"/>
+    <col min="43" max="43" width="9.6328125" customWidth="1"/>
+    <col min="44" max="44" width="11.36328125" customWidth="1"/>
+    <col min="45" max="45" width="14.90625" customWidth="1"/>
+    <col min="46" max="46" width="25.36328125" customWidth="1"/>
+    <col min="47" max="47" width="9.6328125" customWidth="1"/>
+    <col min="48" max="48" width="13.08984375" customWidth="1"/>
     <col min="49" max="49" width="7" customWidth="1"/>
-    <col min="50" max="50" width="7.87272727272727" customWidth="1"/>
-    <col min="51" max="51" width="9.62727272727273" customWidth="1"/>
-    <col min="53" max="53" width="13.1272727272727" customWidth="1"/>
+    <col min="50" max="50" width="7.90625" customWidth="1"/>
+    <col min="51" max="51" width="9.6328125" customWidth="1"/>
+    <col min="53" max="53" width="13.08984375" customWidth="1"/>
     <col min="54" max="54" width="7" customWidth="1"/>
-    <col min="55" max="55" width="7.87272727272727" customWidth="1"/>
-    <col min="56" max="56" width="9.62727272727273" customWidth="1"/>
-    <col min="57" max="57" width="13.1272727272727" customWidth="1"/>
-    <col min="58" max="58" width="16.6272727272727" customWidth="1"/>
-    <col min="59" max="59" width="7.87272727272727" customWidth="1"/>
-    <col min="60" max="60" width="17.5" customWidth="1"/>
-    <col min="61" max="61" width="7.87272727272727" customWidth="1"/>
-    <col min="63" max="63" width="16.6272727272727" customWidth="1"/>
-    <col min="64" max="64" width="11.3727272727273" customWidth="1"/>
-    <col min="66" max="66" width="7.87272727272727" customWidth="1"/>
-    <col min="69" max="69" width="13.1272727272727" customWidth="1"/>
-    <col min="70" max="70" width="7.87272727272727" customWidth="1"/>
-    <col min="71" max="71" width="9.62727272727273" customWidth="1"/>
-    <col min="72" max="72" width="7.87272727272727" customWidth="1"/>
-    <col min="73" max="73" width="13.1272727272727" customWidth="1"/>
-    <col min="74" max="74" width="7.87272727272727" customWidth="1"/>
+    <col min="55" max="55" width="7.90625" customWidth="1"/>
+    <col min="56" max="56" width="9.6328125" customWidth="1"/>
+    <col min="57" max="57" width="13.08984375" customWidth="1"/>
+    <col min="58" max="58" width="16.6328125" customWidth="1"/>
+    <col min="59" max="59" width="7.90625" customWidth="1"/>
+    <col min="60" max="60" width="17.453125" customWidth="1"/>
+    <col min="61" max="61" width="7.90625" customWidth="1"/>
+    <col min="63" max="63" width="16.6328125" customWidth="1"/>
+    <col min="64" max="64" width="11.36328125" customWidth="1"/>
+    <col min="66" max="66" width="7.90625" customWidth="1"/>
+    <col min="69" max="69" width="13.08984375" customWidth="1"/>
+    <col min="70" max="70" width="7.90625" customWidth="1"/>
+    <col min="71" max="71" width="9.6328125" customWidth="1"/>
+    <col min="72" max="72" width="7.90625" customWidth="1"/>
+    <col min="73" max="73" width="13.08984375" customWidth="1"/>
+    <col min="74" max="74" width="7.90625" customWidth="1"/>
     <col min="75" max="75" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74">
+    <row r="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1642,7 +1033,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:74">
+    <row r="2" spans="1:74" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>74</v>
       </c>
@@ -1671,7 +1062,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:74">
+    <row r="3" spans="1:74" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>81</v>
       </c>
@@ -1700,7 +1091,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:74">
+    <row r="4" spans="1:74" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>85</v>
       </c>
@@ -1729,7 +1120,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:74">
+    <row r="5" spans="1:74" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>91</v>
       </c>
@@ -1758,7 +1149,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:74">
+    <row r="6" spans="1:74" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>95</v>
       </c>
@@ -1787,7 +1178,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:74">
+    <row r="7" spans="1:74" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>97</v>
       </c>
@@ -1816,7 +1207,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:74">
+    <row r="8" spans="1:74" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>99</v>
       </c>
@@ -1845,7 +1236,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:74">
+    <row r="9" spans="1:74" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>101</v>
       </c>
@@ -1874,7 +1265,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:74">
+    <row r="10" spans="1:74" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>103</v>
       </c>
@@ -1903,7 +1294,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:74">
+    <row r="11" spans="1:74" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>105</v>
       </c>
@@ -1932,7 +1323,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:74">
+    <row r="12" spans="1:74" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>109</v>
       </c>
@@ -1961,7 +1352,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:74">
+    <row r="13" spans="1:74" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>111</v>
       </c>
@@ -1991,7 +1382,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>